--- a/Analysis_Output/Final_excel_generated.xlsx
+++ b/Analysis_Output/Final_excel_generated.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FinalSummaryTable" displayName="FinalSummaryTable" ref="A1:D6" headerRowCount="1">
-  <autoFilter ref="A1:D6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FinalSummaryTable" displayName="FinalSummaryTable" ref="A1:D17" headerRowCount="1">
+  <autoFilter ref="A1:D17"/>
   <tableColumns count="4">
     <tableColumn id="1" name="filename"/>
     <tableColumn id="2" name="categorization"/>
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
@@ -472,17 +472,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCP1000.pdf</t>
+          <t>CCJ0700.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PDFforms</t>
+          <t>PDF with images</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCP1000.xlsx</t>
+          <t>Final_report_excels\CCJ0700.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCP1003.pdf</t>
+          <t>CCG0134.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCP1003.xlsx</t>
+          <t>Final_report_excels\CCG0134.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCP1004.pdf</t>
+          <t>CCG0135.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCP1004.xlsx</t>
+          <t>Final_report_excels\CCG0135.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCP1005.pdf</t>
+          <t>CCG0136.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCP1005.xlsx</t>
+          <t>Final_report_excels\CCG0136.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCP1007.pdf</t>
+          <t>CCG0137.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -570,12 +570,254 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCP1007.xlsx</t>
+          <t>Final_report_excels\CCG0137.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CCG0813.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0813.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CCG0650.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0650.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CCG0125.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0125.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CCJ0031.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJ0031.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CCG0613.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0613.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CCG0646.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0646.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CCG0815.pdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0815.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GCR2403.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Final_report_excels\GCR2403.xlsx</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRP1101.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Final_report_excels\IRP1101.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MNO705.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Final_report_excels\MNO705.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MSA902.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Final_report_excels\MSA902.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Small</t>
         </is>
       </c>
     </row>

--- a/Analysis_Output/Final_excel_generated.xlsx
+++ b/Analysis_Output/Final_excel_generated.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FinalSummaryTable" displayName="FinalSummaryTable" ref="A1:D17" headerRowCount="1">
-  <autoFilter ref="A1:D17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FinalSummaryTable" displayName="FinalSummaryTable" ref="A1:D194" headerRowCount="1">
+  <autoFilter ref="A1:D194"/>
   <tableColumns count="4">
     <tableColumn id="1" name="filename"/>
     <tableColumn id="2" name="categorization"/>
@@ -438,12 +438,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -472,17 +472,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCJ0700.pdf</t>
+          <t>CCCR0336.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PDF with images</t>
+          <t>PDFforms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCJ0700.xlsx</t>
+          <t>Final_report_excels\CCCR0336.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCG0134.pdf</t>
+          <t>CCJP0108.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0134.xlsx</t>
+          <t>Final_report_excels\CCJP0108.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCG0135.pdf</t>
+          <t>CCCR0333.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0135.xlsx</t>
+          <t>Final_report_excels\CCCR0333.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCG0136.pdf</t>
+          <t>CCJP0604.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0136.xlsx</t>
+          <t>Final_report_excels\CCJP0604.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCG0137.pdf</t>
+          <t>CCJP0631.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0137.xlsx</t>
+          <t>Final_report_excels\CCJP0631.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCG0813.pdf</t>
+          <t>CCJP0652.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,19 +592,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0813.xlsx</t>
+          <t>Final_report_excels\CCJP0652.xlsx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCG0650.pdf</t>
+          <t>CCCH0073.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0650.xlsx</t>
+          <t>Final_report_excels\CCCH0073.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCG0125.pdf</t>
+          <t>CCCO0085.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0125.xlsx</t>
+          <t>Final_report_excels\CCCO0085.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCJ0031.pdf</t>
+          <t>CCCR0090.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -658,19 +658,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCJ0031.xlsx</t>
+          <t>Final_report_excels\CCCR0090.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CCG0613.pdf</t>
+          <t>CCDR0043.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -680,19 +680,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0613.xlsx</t>
+          <t>Final_report_excels\CCDR0043.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CCG0646.pdf</t>
+          <t>CCDR0115.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -702,19 +702,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0646.xlsx</t>
+          <t>Final_report_excels\CCDR0115.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCG0815.pdf</t>
+          <t>CCG0010.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,98 +724,3992 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Final_report_excels\CCG0815.xlsx</t>
+          <t>Final_report_excels\CCG0010.xlsx</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCR2403.pdf</t>
+          <t>CCG0017.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pdf</t>
+          <t>PDFforms</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Final_report_excels\GCR2403.xlsx</t>
+          <t>Final_report_excels\CCG0017.xlsx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRP1101.pdf</t>
+          <t>CCG0029.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pdf</t>
+          <t>PDFforms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Final_report_excels\IRP1101.xlsx</t>
+          <t>Final_report_excels\CCG0029.xlsx</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MNO705.pdf</t>
+          <t>CCG0502.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pdf</t>
+          <t>PDFforms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Final_report_excels\MNO705.xlsx</t>
+          <t>Final_report_excels\CCG0502.xlsx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSA902.pdf</t>
+          <t>CCJP0635.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pdf</t>
+          <t>PDFforms</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Final_report_excels\MSA902.xlsx</t>
+          <t>Final_report_excels\CCJP0635.xlsx</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CCJP0658.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0658.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CCJP0661.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0661.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CCJP0663.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0663.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CCM0058.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0058.xlsx</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CCM0640.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0640.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CCP0008.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0008.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CCSD0693.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCSD0693.xlsx</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VR700.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Final_report_excels\VR700.xlsx</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CCCH0004.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0004.xlsx</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CCCO0030.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0030.xlsx</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CCCR0007.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0007.xlsx</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CCCR0763.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0763.xlsx</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CCDR0001.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0001.xlsx</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CCDR0009.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0009.xlsx</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CCDR0035.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0035.xlsx</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CCDR0069.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0069.xlsx</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CCG0002.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0002.xlsx</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CCG0004.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0004.xlsx</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CCG0033.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0033.xlsx</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CCG0054.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0054.xlsx</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CCG0060.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0060.xlsx</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CCG0103.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0103.xlsx</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CCG0126.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0126.xlsx</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CCG0130.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0130.xlsx</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CCG0132.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0132.xlsx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CCG0133.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0133.xlsx</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CCG0510.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0510.xlsx</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CCG0625.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0625.xlsx</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CCG0812.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0812.xlsx</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CCJ0700.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PDF with images</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJ0700.xlsx</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CCJP0004.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0004.xlsx</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CCJP0020.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0020.xlsx</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CCJP0612.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0612.xlsx</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CCJP0656.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0656.xlsx</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CCL0024.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCL0024.xlsx</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CCL0530.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCL0530.xlsx</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CCM0022.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0022.xlsx</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CCM0067.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0067.xlsx</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CCM0068.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0068.xlsx</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CCM0703.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0703.xlsx</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CCP0002.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0002.xlsx</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CCP0199.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0199.xlsx</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CCP0200.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0200.xlsx</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CCP0201.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0201.xlsx</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CCP0203.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0203.xlsx</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CCP0204.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0204.xlsx</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CCP0207.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0207.xlsx</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CCP0212.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0212.xlsx</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CCP0228.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0228.xlsx</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CCP0232.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0232.xlsx</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CCP0247.pdf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0247.xlsx</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CCP0248.pdf</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0248.xlsx</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CCP0303.pdf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0303.xlsx</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CCP0327.pdf</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0327.xlsx</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CCP0341.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0341.xlsx</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CCP0345.pdf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0345.xlsx</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CCP0378.pdf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0378.xlsx</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CCP0701.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0701.xlsx</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CCP1000.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1000.xlsx</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CCP1010.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1010.xlsx</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CCTR0090.pdf</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCTR0090.xlsx</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CCCO0032.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0032.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CCCR0334.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0334.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CCG0093.pdf</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0093.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CCG0172.pdf</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0172.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CCG0176.pdf</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0176.xlsx</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CCG0807.pdf</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0807.xlsx</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CCJP0662.pdf</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0662.xlsx</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CCM0520.pdf</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0520.xlsx</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CCM0605.pdf</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0605.xlsx</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CCP0009.pdf</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0009.xlsx</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CCP0178.pdf</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0178.xlsx</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CCP0179.pdf</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0179.xlsx</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CCP0213.pdf</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0213.xlsx</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CCP0216.pdf</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0216.xlsx</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CCP0306.pdf</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0306.xlsx</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CCP0307.pdf</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0307.xlsx</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CCP0308.pdf</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0308.xlsx</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CCP0309.pdf</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0309.xlsx</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CCP0314.pdf</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0314.xlsx</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CCP0317.pdf</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0317.xlsx</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CCP0319.pdf</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0319.xlsx</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CCP0320.pdf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0320.xlsx</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CCP0324.pdf</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0324.xlsx</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CCP0328.pdf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0328.xlsx</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CCP0331.pdf</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0331.xlsx</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CCP0337.pdf</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0337.xlsx</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CCP0339.pdf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0339.xlsx</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CCP0342.pdf</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0342.xlsx</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CCP0343.pdf</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0343.xlsx</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CCP0356.pdf</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0356.xlsx</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CCP0357.pdf</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0357.xlsx</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CCP0359.pdf</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0359.xlsx</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CCP0360.pdf</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0360.xlsx</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CCP0361.pdf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0361.xlsx</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CCP0366.pdf</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0366.xlsx</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CCP0368.pdf</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0368.xlsx</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CCP0379.pdf</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0379.xlsx</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CCP0380.pdf</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0380.xlsx</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CCP0382.pdf</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0382.xlsx</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CCP0383.pdf</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0383.xlsx</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CCP0385.pdf</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0385.xlsx</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CCP0386.pdf</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0386.xlsx</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CCP0387.pdf</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0387.xlsx</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CCP0388.pdf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0388.xlsx</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CCP0389.pdf</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0389.xlsx</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CCP0421.pdf</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0421.xlsx</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CCP0600.pdf</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0600.xlsx</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CCP0612.pdf</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0612.xlsx</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CCP1003.pdf</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1003.xlsx</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CCP1004.pdf</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1004.xlsx</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CCP1005.pdf</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1005.xlsx</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CCP1007.pdf</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1007.xlsx</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CCP1008.pdf</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1008.xlsx</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CCP1009.pdf</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1009.xlsx</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CCP1013.pdf</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1013.xlsx</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CCP1014.pdf</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1014.xlsx</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CCP1015.pdf</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1015.xlsx</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CCP1017.pdf</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1017.xlsx</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CCP1020.pdf</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1020.xlsx</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CCP1022.pdf</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1022.xlsx</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CCP1023.pdf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1023.xlsx</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CCCR0100.pdf</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PDF with images</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0100.xlsx</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CCG0134.pdf</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0134.xlsx</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CCG0135.pdf</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0135.xlsx</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CCG0136.pdf</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0136.xlsx</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CCG0143.pdf</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0143.xlsx</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CCG0144.pdf</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0144.xlsx</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CCG0813.pdf</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0813.xlsx</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CCCO0027.pdf</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0027.xlsx</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CCCO0203.pdf</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0203.xlsx</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CCG0650.pdf</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0650.xlsx</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CCDR0006.pdf</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0006.xlsx</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CCG0082.pdf</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0082.xlsx</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CCA0024.pdf</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCA0024.xlsx</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CCG0648.pdf</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0648.xlsx</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CCP0374.pdf</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0374.xlsx</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CCDR0019.pdf</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0019.xlsx</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CCDV0012.pdf</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDV0012.xlsx</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CCJP0622.pdf</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0622.xlsx</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CCP1011.pdf</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1011.xlsx</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CCP1024.pdf</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP1024.xlsx</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CCCH0317.pdf</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0317.xlsx</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CCCO0005.pdf</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0005.xlsx</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CCG0052.pdf</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0052.xlsx</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CCJP0633.pdf</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0633.xlsx</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CCM0641.pdf</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0641.xlsx</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CCTR0030.pdf</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCTR0030.xlsx</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CCM0062.pdf</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0062.xlsx</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CCM0702.pdf</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0702.xlsx</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CCCO0062.pdf</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0062.xlsx</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CCCR0325.pdf</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0325.xlsx</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CCSD0618.pdf</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCSD0618.xlsx</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CCCR0324.pdf</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0324.xlsx</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CCDR0022.pdf</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCDR0022.xlsx</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CCSD0007.pdf</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCSD0007.xlsx</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CCG0649.pdf</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0649.xlsx</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CCM0050.pdf</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0050.xlsx</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CCM0704.pdf</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0704.xlsx</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CCP0305.pdf</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCP0305.xlsx</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CCTR0506.pdf</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCTR0506.xlsx</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CCCH0019.pdf</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0019.xlsx</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CCCH0048.pdf</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0048.xlsx</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CCCH0100.pdf</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0100.xlsx</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CCCH0102.pdf</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCH0102.xlsx</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CCCR0511.pdf</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCR0511.xlsx</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CCG0073.pdf</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0073.xlsx</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CCG0124.pdf</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0124.xlsx</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CCG0600.pdf</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0600.xlsx</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CCJP0041.pdf</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCJP0041.xlsx</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CCM0013.pdf</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0013.xlsx</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CCCO0023.pdf</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCCO0023.xlsx</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CCG0038.pdf</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0038.xlsx</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CCG0514.pdf</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0514.xlsx</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CCG0522.pdf</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0522.xlsx</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CCG0647.pdf</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCG0647.xlsx</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CCM0141.pdf</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PDFforms</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Final_report_excels\CCM0141.xlsx</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
